--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4587,6 +4587,2242 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128686526</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>639364</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7192333</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128686604</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>639536</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7192152</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128686537</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>639624</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7192110</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128686536</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>639651</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7192110</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128686530</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>639618</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7192302</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128686533</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>639460</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7192329</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128686529</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>639516</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7192394</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128686531</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>639615</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7192173</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128686532</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>639533</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7192279</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128686535</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>639438</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7192196</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128686538</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>639550</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7192132</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128686527</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>639436</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7192394</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128693376</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>639463</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7192184</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Bohål i asp</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128686603</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>639410</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7192214</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128685996</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>639205</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7192197</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128686576</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>639560</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7192069</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128686534</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>639319</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7192216</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128686608</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>639279</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7192113</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128686528</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>639685</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7192229</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128686539</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>639369</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7192265</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128686577</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>639319</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7192216</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128686575</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Rörmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>639524</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7192361</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4890,7 +4890,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128686536</v>
+        <v>128686530</v>
       </c>
       <c r="B43" t="n">
         <v>98588</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>639651</v>
+        <v>639618</v>
       </c>
       <c r="R43" t="n">
-        <v>7192110</v>
+        <v>7192302</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128686530</v>
+        <v>128686536</v>
       </c>
       <c r="B44" t="n">
         <v>98588</v>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>639618</v>
+        <v>639651</v>
       </c>
       <c r="R44" t="n">
-        <v>7192302</v>
+        <v>7192110</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686531</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
         <v>98588</v>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639615</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192173</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686532</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
         <v>98588</v>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639533</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192279</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686535</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
         <v>98588</v>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639438</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192196</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128686603</v>
+        <v>128685996</v>
       </c>
       <c r="B53" t="n">
         <v>57689</v>
@@ -5909,21 +5909,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639410</v>
+        <v>639205</v>
       </c>
       <c r="R53" t="n">
-        <v>7192214</v>
+        <v>7192197</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685996</v>
+        <v>128686576</v>
       </c>
       <c r="B54" t="n">
         <v>57689</v>
@@ -6020,7 +6023,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6030,10 +6033,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639205</v>
+        <v>639560</v>
       </c>
       <c r="R54" t="n">
-        <v>7192197</v>
+        <v>7192069</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6070,7 +6073,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,7 +6100,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128686576</v>
+        <v>128686603</v>
       </c>
       <c r="B55" t="n">
         <v>57689</v>
@@ -6126,24 +6129,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639560</v>
+        <v>639410</v>
       </c>
       <c r="R55" t="n">
-        <v>7192069</v>
+        <v>7192214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128686577</v>
+        <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6629,34 +6629,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639319</v>
+        <v>639524</v>
       </c>
       <c r="R60" t="n">
-        <v>7192216</v>
+        <v>7192361</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6689,6 +6697,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6715,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128686575</v>
+        <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6726,42 +6739,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639524</v>
+        <v>639319</v>
       </c>
       <c r="R61" t="n">
-        <v>7192361</v>
+        <v>7192216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,11 +6799,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,45 +5181,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686529</v>
+        <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639516</v>
+        <v>639550</v>
       </c>
       <c r="R46" t="n">
-        <v>7192394</v>
+        <v>7192132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5257,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5288,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686535</v>
+        <v>128686529</v>
       </c>
       <c r="B47" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639438</v>
+        <v>639516</v>
       </c>
       <c r="R47" t="n">
-        <v>7192196</v>
+        <v>7192394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,10 +5385,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686531</v>
+        <v>128686535</v>
       </c>
       <c r="B48" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639615</v>
+        <v>639438</v>
       </c>
       <c r="R48" t="n">
-        <v>7192173</v>
+        <v>7192196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,10 +5482,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686531</v>
       </c>
       <c r="B49" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5507,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639615</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192173</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6304,53 +6304,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128686608</v>
+        <v>128686528</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>639279</v>
+        <v>639685</v>
       </c>
       <c r="R57" t="n">
-        <v>7192113</v>
+        <v>7192229</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6383,11 +6375,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6414,45 +6401,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128686528</v>
+        <v>128686608</v>
       </c>
       <c r="B58" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>639685</v>
+        <v>639279</v>
       </c>
       <c r="R58" t="n">
-        <v>7192229</v>
+        <v>7192113</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6485,6 +6480,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128686575</v>
+        <v>128686577</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6629,42 +6629,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639524</v>
+        <v>639319</v>
       </c>
       <c r="R60" t="n">
-        <v>7192361</v>
+        <v>7192216</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6697,11 +6689,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6728,10 +6715,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128686577</v>
+        <v>128686575</v>
       </c>
       <c r="B61" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6739,34 +6726,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639319</v>
+        <v>639524</v>
       </c>
       <c r="R61" t="n">
-        <v>7192216</v>
+        <v>7192361</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6799,6 +6794,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>128686529</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>128686535</v>
       </c>
       <c r="B48" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>128686531</v>
       </c>
       <c r="B49" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685996</v>
+        <v>128686576</v>
       </c>
       <c r="B53" t="n">
         <v>57689</v>
@@ -5913,7 +5913,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639205</v>
+        <v>639560</v>
       </c>
       <c r="R53" t="n">
-        <v>7192197</v>
+        <v>7192069</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5990,7 +5990,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128686576</v>
+        <v>128686603</v>
       </c>
       <c r="B54" t="n">
         <v>57689</v>
@@ -6019,24 +6019,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639560</v>
+        <v>639410</v>
       </c>
       <c r="R54" t="n">
-        <v>7192069</v>
+        <v>7192214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6073,7 +6070,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6100,7 +6097,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128686603</v>
+        <v>128685996</v>
       </c>
       <c r="B55" t="n">
         <v>57689</v>
@@ -6129,21 +6126,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639410</v>
+        <v>639205</v>
       </c>
       <c r="R55" t="n">
-        <v>7192214</v>
+        <v>7192197</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6304,45 +6304,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128686528</v>
+        <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>639685</v>
+        <v>639279</v>
       </c>
       <c r="R57" t="n">
-        <v>7192229</v>
+        <v>7192113</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6375,6 +6383,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,53 +6414,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128686608</v>
+        <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>639279</v>
+        <v>639685</v>
       </c>
       <c r="R58" t="n">
-        <v>7192113</v>
+        <v>7192229</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6480,11 +6485,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128686577</v>
+        <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6629,34 +6629,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639319</v>
+        <v>639524</v>
       </c>
       <c r="R60" t="n">
-        <v>7192216</v>
+        <v>7192361</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6689,6 +6697,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6715,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128686575</v>
+        <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6726,42 +6739,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639524</v>
+        <v>639319</v>
       </c>
       <c r="R61" t="n">
-        <v>7192361</v>
+        <v>7192216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,11 +6799,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686529</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639516</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192394</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128693376</v>
       </c>
       <c r="B52" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128686576</v>
+        <v>128685996</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639560</v>
+        <v>639205</v>
       </c>
       <c r="R53" t="n">
-        <v>7192069</v>
+        <v>7192197</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5990,10 +5990,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128686603</v>
+        <v>128686576</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6019,21 +6019,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639410</v>
+        <v>639560</v>
       </c>
       <c r="R54" t="n">
-        <v>7192214</v>
+        <v>7192069</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6070,7 +6073,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6100,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685996</v>
+        <v>128686603</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6126,24 +6129,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639205</v>
+        <v>639410</v>
       </c>
       <c r="R55" t="n">
-        <v>7192197</v>
+        <v>7192214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128686539</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -5181,45 +5181,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686529</v>
+        <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639516</v>
+        <v>639550</v>
       </c>
       <c r="R46" t="n">
-        <v>7192394</v>
+        <v>7192132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5257,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,7 +5288,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686535</v>
+        <v>128686529</v>
       </c>
       <c r="B47" t="n">
         <v>98619</v>
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639438</v>
+        <v>639516</v>
       </c>
       <c r="R47" t="n">
-        <v>7192196</v>
+        <v>7192394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,7 +5385,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686531</v>
+        <v>128686535</v>
       </c>
       <c r="B48" t="n">
         <v>98619</v>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639615</v>
+        <v>639438</v>
       </c>
       <c r="R48" t="n">
-        <v>7192173</v>
+        <v>7192196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5482,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686531</v>
       </c>
       <c r="B49" t="n">
         <v>98619</v>
@@ -5507,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639615</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192173</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>128686529</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>128686535</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>128686531</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686531</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639615</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192173</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686529</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639516</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192394</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686529</v>
       </c>
       <c r="B48" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639516</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98625</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4686,50 +4686,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R41" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,11 +4757,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4793,45 +4783,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R42" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,6 +4859,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5181,7 +5181,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686531</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
         <v>98632</v>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639615</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192173</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686529</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
         <v>98632</v>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639516</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192394</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6304,53 +6304,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128686608</v>
+        <v>128686528</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>639279</v>
+        <v>639685</v>
       </c>
       <c r="R57" t="n">
-        <v>7192113</v>
+        <v>7192229</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6383,11 +6375,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6414,45 +6401,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128686528</v>
+        <v>128686608</v>
       </c>
       <c r="B58" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>639685</v>
+        <v>639279</v>
       </c>
       <c r="R58" t="n">
-        <v>7192229</v>
+        <v>7192113</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6485,6 +6480,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4686,45 +4686,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R41" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,6 +4762,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4783,50 +4793,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R42" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,11 +4864,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5181,45 +5181,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686529</v>
+        <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639516</v>
+        <v>639550</v>
       </c>
       <c r="R46" t="n">
-        <v>7192394</v>
+        <v>7192132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5257,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,7 +5288,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686535</v>
+        <v>128686529</v>
       </c>
       <c r="B47" t="n">
         <v>98632</v>
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639438</v>
+        <v>639516</v>
       </c>
       <c r="R47" t="n">
-        <v>7192196</v>
+        <v>7192394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,7 +5385,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686531</v>
+        <v>128686535</v>
       </c>
       <c r="B48" t="n">
         <v>98632</v>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639615</v>
+        <v>639438</v>
       </c>
       <c r="R48" t="n">
-        <v>7192173</v>
+        <v>7192196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5482,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686531</v>
       </c>
       <c r="B49" t="n">
         <v>98632</v>
@@ -5507,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639615</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192173</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,45 +6304,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128686528</v>
+        <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>639685</v>
+        <v>639279</v>
       </c>
       <c r="R57" t="n">
-        <v>7192229</v>
+        <v>7192113</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6375,6 +6383,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,53 +6414,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128686608</v>
+        <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>639279</v>
+        <v>639685</v>
       </c>
       <c r="R58" t="n">
-        <v>7192113</v>
+        <v>7192229</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6480,11 +6485,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4686,50 +4686,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R41" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,11 +4757,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4793,45 +4783,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R42" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,6 +4859,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686529</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639516</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192394</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>57720</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128693376</v>
       </c>
       <c r="B52" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685996</v>
+        <v>128686576</v>
       </c>
       <c r="B53" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639205</v>
+        <v>639560</v>
       </c>
       <c r="R53" t="n">
-        <v>7192197</v>
+        <v>7192069</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5990,10 +5990,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128686576</v>
+        <v>128686603</v>
       </c>
       <c r="B54" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6019,24 +6019,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639560</v>
+        <v>639410</v>
       </c>
       <c r="R54" t="n">
-        <v>7192069</v>
+        <v>7192214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6073,7 +6070,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6100,10 +6097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128686603</v>
+        <v>128685996</v>
       </c>
       <c r="B55" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6129,21 +6126,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639410</v>
+        <v>639205</v>
       </c>
       <c r="R55" t="n">
-        <v>7192214</v>
+        <v>7192197</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128686539</v>
       </c>
       <c r="B59" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4686,45 +4686,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R41" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,6 +4762,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4783,50 +4793,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R42" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,11 +4864,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128686530</v>
+        <v>128686536</v>
       </c>
       <c r="B43" t="n">
         <v>98636</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>639618</v>
+        <v>639651</v>
       </c>
       <c r="R43" t="n">
-        <v>7192302</v>
+        <v>7192110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128686536</v>
+        <v>128686530</v>
       </c>
       <c r="B44" t="n">
         <v>98636</v>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>639651</v>
+        <v>639618</v>
       </c>
       <c r="R44" t="n">
-        <v>7192110</v>
+        <v>7192302</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,45 +5181,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686529</v>
+        <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639516</v>
+        <v>639550</v>
       </c>
       <c r="R46" t="n">
-        <v>7192394</v>
+        <v>7192132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5257,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,7 +5288,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B47" t="n">
         <v>98636</v>
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R47" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,7 +5385,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686531</v>
+        <v>128686535</v>
       </c>
       <c r="B48" t="n">
         <v>98636</v>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639615</v>
+        <v>639438</v>
       </c>
       <c r="R48" t="n">
-        <v>7192173</v>
+        <v>7192196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686529</v>
       </c>
       <c r="B50" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639516</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192394</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128686576</v>
+        <v>128685996</v>
       </c>
       <c r="B53" t="n">
         <v>57720</v>
@@ -5913,7 +5913,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639560</v>
+        <v>639205</v>
       </c>
       <c r="R53" t="n">
-        <v>7192069</v>
+        <v>7192197</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5990,7 +5990,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128686603</v>
+        <v>128686576</v>
       </c>
       <c r="B54" t="n">
         <v>57720</v>
@@ -6019,21 +6019,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639410</v>
+        <v>639560</v>
       </c>
       <c r="R54" t="n">
-        <v>7192214</v>
+        <v>7192069</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6070,7 +6073,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,7 +6100,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685996</v>
+        <v>128686603</v>
       </c>
       <c r="B55" t="n">
         <v>57720</v>
@@ -6126,24 +6129,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639205</v>
+        <v>639410</v>
       </c>
       <c r="R55" t="n">
-        <v>7192197</v>
+        <v>7192214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4890,7 +4890,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128686536</v>
+        <v>128686530</v>
       </c>
       <c r="B43" t="n">
         <v>98636</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>639651</v>
+        <v>639618</v>
       </c>
       <c r="R43" t="n">
-        <v>7192110</v>
+        <v>7192302</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128686530</v>
+        <v>128686536</v>
       </c>
       <c r="B44" t="n">
         <v>98636</v>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>639618</v>
+        <v>639651</v>
       </c>
       <c r="R44" t="n">
-        <v>7192302</v>
+        <v>7192110</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686531</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639615</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192173</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,45 +5278,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686531</v>
+        <v>128686538</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639615</v>
+        <v>639550</v>
       </c>
       <c r="R47" t="n">
-        <v>7192173</v>
+        <v>7192132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,6 +5354,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5482,7 +5482,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686529</v>
       </c>
       <c r="B49" t="n">
         <v>98636</v>
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639516</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686529</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
         <v>98636</v>
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639516</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192394</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128686576</v>
+        <v>128686603</v>
       </c>
       <c r="B54" t="n">
         <v>57720</v>
@@ -6019,24 +6019,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639560</v>
+        <v>639410</v>
       </c>
       <c r="R54" t="n">
-        <v>7192069</v>
+        <v>7192214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6073,7 +6070,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6100,7 +6097,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128686603</v>
+        <v>128686576</v>
       </c>
       <c r="B55" t="n">
         <v>57720</v>
@@ -6129,21 +6126,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639410</v>
+        <v>639560</v>
       </c>
       <c r="R55" t="n">
-        <v>7192214</v>
+        <v>7192069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128686575</v>
+        <v>128686577</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6629,42 +6629,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639524</v>
+        <v>639319</v>
       </c>
       <c r="R60" t="n">
-        <v>7192361</v>
+        <v>7192216</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6697,11 +6689,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6728,10 +6715,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128686577</v>
+        <v>128686575</v>
       </c>
       <c r="B61" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6739,34 +6726,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639319</v>
+        <v>639524</v>
       </c>
       <c r="R61" t="n">
-        <v>7192216</v>
+        <v>7192361</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6799,6 +6794,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686531</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639615</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192173</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5278,50 +5278,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686538</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639550</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192132</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5354,11 +5349,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686529</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639516</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192394</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128693376</v>
       </c>
       <c r="B52" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128685996</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128686603</v>
+        <v>128686576</v>
       </c>
       <c r="B54" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6019,21 +6019,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639410</v>
+        <v>639560</v>
       </c>
       <c r="R54" t="n">
-        <v>7192214</v>
+        <v>7192069</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6070,7 +6073,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6100,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128686576</v>
+        <v>128686603</v>
       </c>
       <c r="B55" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6126,24 +6129,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>639560</v>
+        <v>639410</v>
       </c>
       <c r="R55" t="n">
-        <v>7192069</v>
+        <v>7192214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Bohål några meter upp på asp. Se bild. Osäker artbestämning p.g.a. för högt upp för att mäta diameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128686539</v>
       </c>
       <c r="B59" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128686577</v>
+        <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57880</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6629,34 +6629,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639319</v>
+        <v>639524</v>
       </c>
       <c r="R60" t="n">
-        <v>7192216</v>
+        <v>7192361</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6689,6 +6697,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6715,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128686575</v>
+        <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6726,42 +6739,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639524</v>
+        <v>639319</v>
       </c>
       <c r="R61" t="n">
-        <v>7192361</v>
+        <v>7192216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,11 +6799,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -6618,10 +6618,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128686577</v>
+        <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6629,34 +6629,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639319</v>
+        <v>639524</v>
       </c>
       <c r="R60" t="n">
-        <v>7192216</v>
+        <v>7192361</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6689,6 +6697,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6715,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128686575</v>
+        <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6726,42 +6739,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639524</v>
+        <v>639319</v>
       </c>
       <c r="R61" t="n">
-        <v>7192361</v>
+        <v>7192216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,11 +6799,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bohål två meter upp på asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686529</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639516</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192394</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,45 +5181,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686529</v>
+        <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639516</v>
+        <v>639550</v>
       </c>
       <c r="R46" t="n">
-        <v>7192394</v>
+        <v>7192132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5257,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5288,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686535</v>
+        <v>128686529</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639438</v>
+        <v>639516</v>
       </c>
       <c r="R47" t="n">
-        <v>7192196</v>
+        <v>7192394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,10 +5385,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686531</v>
+        <v>128686535</v>
       </c>
       <c r="B48" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639615</v>
+        <v>639438</v>
       </c>
       <c r="R48" t="n">
-        <v>7192173</v>
+        <v>7192196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,10 +5482,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686531</v>
       </c>
       <c r="B49" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5507,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639615</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192173</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,7 +5278,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686529</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
         <v>98659</v>
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639516</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192394</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,7 +5375,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
         <v>98659</v>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
         <v>98659</v>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,53 +6304,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128686608</v>
+        <v>128686528</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>639279</v>
+        <v>639685</v>
       </c>
       <c r="R57" t="n">
-        <v>7192113</v>
+        <v>7192229</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6383,11 +6375,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6414,45 +6401,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128686528</v>
+        <v>128686608</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>639685</v>
+        <v>639279</v>
       </c>
       <c r="R58" t="n">
-        <v>7192229</v>
+        <v>7192113</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6485,6 +6480,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -6304,45 +6304,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128686528</v>
+        <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>639685</v>
+        <v>639279</v>
       </c>
       <c r="R57" t="n">
-        <v>7192229</v>
+        <v>7192113</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6375,6 +6383,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,53 +6414,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128686608</v>
+        <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>639279</v>
+        <v>639685</v>
       </c>
       <c r="R58" t="n">
-        <v>7192113</v>
+        <v>7192229</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6480,11 +6485,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4686,50 +4686,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R41" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,11 +4757,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4793,45 +4783,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R42" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,6 +4859,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5181,45 +5181,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686529</v>
+        <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639516</v>
+        <v>639550</v>
       </c>
       <c r="R46" t="n">
-        <v>7192394</v>
+        <v>7192132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5257,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5375,7 +5385,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B48" t="n">
         <v>98659</v>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R48" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5482,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686529</v>
       </c>
       <c r="B49" t="n">
         <v>98659</v>
@@ -5507,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639516</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686531</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639615</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4686,45 +4686,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R41" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,6 +4762,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4783,50 +4793,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R42" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,11 +4864,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4893,7 +4893,7 @@
         <v>128686530</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>128686536</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>128686538</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686535</v>
+        <v>128686529</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639438</v>
+        <v>639516</v>
       </c>
       <c r="R47" t="n">
-        <v>7192196</v>
+        <v>7192394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686532</v>
+        <v>128686535</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639533</v>
+        <v>639438</v>
       </c>
       <c r="R48" t="n">
-        <v>7192279</v>
+        <v>7192196</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,10 +5482,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686529</v>
+        <v>128686531</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639516</v>
+        <v>639615</v>
       </c>
       <c r="R49" t="n">
-        <v>7192394</v>
+        <v>7192173</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,10 +5579,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128693376</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128685996</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>128686576</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128686603</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128686539</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4686,50 +4686,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R41" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,11 +4757,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4793,45 +4783,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R42" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,6 +4859,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5181,50 +5181,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128686538</v>
+        <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639550</v>
+        <v>639516</v>
       </c>
       <c r="R46" t="n">
-        <v>7192132</v>
+        <v>7192394</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5288,7 +5278,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128686529</v>
+        <v>128686535</v>
       </c>
       <c r="B47" t="n">
         <v>98669</v>
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639516</v>
+        <v>639438</v>
       </c>
       <c r="R47" t="n">
-        <v>7192394</v>
+        <v>7192196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,7 +5375,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128686535</v>
+        <v>128686531</v>
       </c>
       <c r="B48" t="n">
         <v>98669</v>
@@ -5420,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639438</v>
+        <v>639615</v>
       </c>
       <c r="R48" t="n">
-        <v>7192196</v>
+        <v>7192173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686531</v>
+        <v>128686532</v>
       </c>
       <c r="B49" t="n">
         <v>98669</v>
@@ -5517,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639615</v>
+        <v>639533</v>
       </c>
       <c r="R49" t="n">
-        <v>7192173</v>
+        <v>7192279</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,45 +5569,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R50" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4686,45 +4686,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128686537</v>
+        <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>639624</v>
+        <v>639536</v>
       </c>
       <c r="R41" t="n">
-        <v>7192110</v>
+        <v>7192152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,6 +4762,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4783,50 +4793,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128686604</v>
+        <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>639536</v>
+        <v>639624</v>
       </c>
       <c r="R42" t="n">
-        <v>7192152</v>
+        <v>7192110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,11 +4864,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 38802-2025 artfynd.xlsx
+++ b/artfynd/A 38802-2025 artfynd.xlsx
@@ -4592,7 +4592,7 @@
         <v>128686526</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>128686604</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>128686537</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128686530</v>
+        <v>128686536</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>639618</v>
+        <v>639651</v>
       </c>
       <c r="R43" t="n">
-        <v>7192302</v>
+        <v>7192110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128686536</v>
+        <v>128686530</v>
       </c>
       <c r="B44" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>639651</v>
+        <v>639618</v>
       </c>
       <c r="R44" t="n">
-        <v>7192110</v>
+        <v>7192302</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
         <v>128686533</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>128686529</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>128686535</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>128686531</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5472,45 +5472,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128686532</v>
+        <v>128686538</v>
       </c>
       <c r="B49" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639533</v>
+        <v>639550</v>
       </c>
       <c r="R49" t="n">
-        <v>7192279</v>
+        <v>7192132</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,6 +5548,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,50 +5579,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128686538</v>
+        <v>128686532</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rörmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639550</v>
+        <v>639533</v>
       </c>
       <c r="R50" t="n">
-        <v>7192132</v>
+        <v>7192279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,11 +5650,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,7 +5679,7 @@
         <v>128686527</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128693376</v>
       </c>
       <c r="B52" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128685996</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>128686576</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128686603</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>128686534</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>128686608</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>128686528</v>
       </c>
       <c r="B58" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128686539</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128686575</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>128686577</v>
       </c>
       <c r="B61" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
